--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit1.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit1.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
+          <t>遵收</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>尊收</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
           <t>遵守</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>尊收</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>遵收</t>
         </is>
       </c>
       <c r="G9" s="22" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -782,17 +782,17 @@
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
+          <t>字形怪</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>意思怪</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
           <t>讀音怪</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>字形怪</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>意思怪</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" s="1" t="n"/>
@@ -817,12 +817,12 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
+          <t>冇錯 ✅</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
           <t>有錯 🙅</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>冇錯 ✅</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
+          <t>急須</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
           <t>急需</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>急須</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -884,17 +884,17 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
+          <t>尋找</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>立刻</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
           <t>媽媽</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>尋找</t>
-        </is>
-      </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>立刻</t>
         </is>
       </c>
       <c r="G14" s="25" t="n">
@@ -918,12 +918,12 @@
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
+          <t>志</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
           <t>標</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>志</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -949,22 +949,22 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
+          <t>標志</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>標示</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
           <t>標誌</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>標志</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>標記</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>標示</t>
         </is>
       </c>
       <c r="G16" s="25" t="n">
@@ -972,7 +972,7 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" s="1" t="n"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
+          <t>志</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
           <t>標</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>志</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
+          <t>字形怪</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
           <t>讀音怪</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>字形怪</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
+          <t>冇錯 ✅</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
           <t>有錯 🙅</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>冇錯 ✅</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
+          <t>籃</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
           <t>藍</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>籃</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -1116,22 +1116,22 @@
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
+          <t>媽媽</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>幫忙</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
           <t>尋找</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>媽媽</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>立刻</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>幫忙</t>
         </is>
       </c>
       <c r="G21" s="25" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
+          <t>經</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
           <t>以</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>經</t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H22" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" s="1" t="n"/>
@@ -1186,22 +1186,22 @@
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
+          <t>邊綠</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>邊緣</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>邊源</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
           <t>邊錄</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>邊綠</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>邊緣</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
-        <is>
-          <t>邊源</t>
         </is>
       </c>
       <c r="G23" s="25" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" s="1" t="n"/>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
+          <t>字形怪</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
           <t>讀音怪</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>字形怪</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
+          <t>記事薄</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
           <t>記事簿</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>記事薄</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" s="1" t="n"/>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
+          <t>媽媽</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>立刻</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>幫忙</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
           <t>尋找</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>幫忙</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>媽媽</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>立刻</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
+          <t>緝</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
           <t>編</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>緝</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
